--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="444" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -131,9 +131,6 @@
     <t>PEREZ ISLAS ANA LAURA</t>
   </si>
   <si>
-    <t>PUGA CABRERA ALEJANDRO</t>
-  </si>
-  <si>
     <t>QUESADA OLGUIN JARED DE JESUS</t>
   </si>
   <si>
@@ -197,18 +194,18 @@
     <t>Villanueva Morales Luis Arturo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Pesce Bautista Victor Manuel</t>
+  </si>
+  <si>
     <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -251,7 +248,7 @@
     <t>PARRA</t>
   </si>
   <si>
-    <t>PUGA</t>
+    <t>PUGA CABRERA</t>
   </si>
   <si>
     <t>QUESADA</t>
@@ -294,9 +291,6 @@
   </si>
   <si>
     <t>FLORES</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
   </si>
   <si>
     <t>OLGUIN</t>
@@ -831,7 +825,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y39"/>
+  <dimension ref="A1:Y38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -983,13 +977,13 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -1019,13 +1013,13 @@
         <v>-1</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -1060,13 +1054,13 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
         <v>-1</v>
@@ -1096,13 +1090,13 @@
         <v>-1</v>
       </c>
       <c r="V5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>6</v>
@@ -1137,13 +1131,13 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
         <v>-1</v>
@@ -1173,10 +1167,10 @@
         <v>6</v>
       </c>
       <c r="V6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>6</v>
@@ -1214,13 +1208,13 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1250,13 +1244,13 @@
         <v>-1</v>
       </c>
       <c r="V7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y7">
         <v>10</v>
@@ -1288,16 +1282,16 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M8">
         <v>-1</v>
@@ -1327,7 +1321,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1365,16 +1359,16 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1404,13 +1398,13 @@
         <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y9">
         <v>9</v>
@@ -1442,16 +1436,16 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1478,16 +1472,16 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>7</v>
@@ -1519,16 +1513,16 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J11">
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
         <v>-1</v>
@@ -1561,10 +1555,10 @@
         <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
         <v>7</v>
@@ -1599,13 +1593,13 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1673,13 +1667,13 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
         <v>-1</v>
@@ -1709,7 +1703,7 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>8</v>
@@ -1750,16 +1744,16 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1795,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>9</v>
@@ -1827,16 +1821,16 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
         <v>-1</v>
@@ -1869,7 +1863,7 @@
         <v>6</v>
       </c>
       <c r="W15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X15">
         <v>6</v>
@@ -1907,13 +1901,13 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
         <v>-1</v>
@@ -1949,7 +1943,7 @@
         <v>9</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
         <v>8</v>
@@ -1981,16 +1975,16 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -2061,13 +2055,13 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>-1</v>
@@ -2123,7 +2117,7 @@
         <v>7</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F19">
         <v>6</v>
@@ -2141,10 +2135,10 @@
         <v>-1</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M19">
         <v>-1</v>
@@ -2177,10 +2171,10 @@
         <v>7</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2212,16 +2206,16 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2248,16 +2242,16 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V20">
         <v>6</v>
       </c>
       <c r="W20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y20">
         <v>6</v>
@@ -2289,16 +2283,16 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>-1</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2331,7 +2325,7 @@
         <v>6</v>
       </c>
       <c r="W21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>9</v>
@@ -2366,16 +2360,16 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2402,13 +2396,13 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X22">
         <v>7</v>
@@ -2443,16 +2437,16 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2488,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y23">
         <v>6</v>
@@ -2523,13 +2517,13 @@
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
         <v>-1</v>
@@ -2559,7 +2553,7 @@
         <v>-1</v>
       </c>
       <c r="V24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2600,13 +2594,13 @@
         <v>-1</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M25">
         <v>-1</v>
@@ -2636,13 +2630,13 @@
         <v>-1</v>
       </c>
       <c r="V25">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y25">
         <v>7</v>
@@ -2674,16 +2668,16 @@
         <v>-1</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>-1</v>
@@ -2719,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2754,13 +2748,13 @@
         <v>-1</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
         <v>-1</v>
@@ -2790,13 +2784,13 @@
         <v>-1</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2828,16 +2822,16 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2864,10 +2858,10 @@
         <v>7</v>
       </c>
       <c r="U28">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W28">
         <v>9</v>
@@ -2884,22 +2878,22 @@
         <v>37</v>
       </c>
       <c r="B29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29">
         <v>-1</v>
       </c>
       <c r="D29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H29">
         <v>-1</v>
@@ -2908,13 +2902,13 @@
         <v>-1</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>-1</v>
@@ -2938,22 +2932,22 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U29">
         <v>-1</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W29">
         <v>9</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y29">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2961,22 +2955,22 @@
         <v>38</v>
       </c>
       <c r="B30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D30">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F30">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H30">
         <v>-1</v>
@@ -2985,13 +2979,13 @@
         <v>-1</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>-1</v>
@@ -3015,22 +3009,22 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>7</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -3038,37 +3032,37 @@
         <v>39</v>
       </c>
       <c r="B31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31">
         <v>6</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H31">
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
         <v>-1</v>
@@ -3092,22 +3086,22 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>6</v>
       </c>
       <c r="W31">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3118,19 +3112,19 @@
         <v>6</v>
       </c>
       <c r="C32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D32">
         <v>6</v>
       </c>
       <c r="E32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G32">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H32">
         <v>-1</v>
@@ -3139,13 +3133,13 @@
         <v>-1</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3172,19 +3166,19 @@
         <v>6</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="X32">
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3192,34 +3186,34 @@
         <v>41</v>
       </c>
       <c r="B33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G33">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H33">
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L33">
         <v>-1</v>
@@ -3246,22 +3240,22 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3272,34 +3266,34 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D34">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E34">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G34">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="H34">
         <v>-1</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3326,19 +3320,19 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W34">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="X34">
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>6</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3346,37 +3340,37 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="C35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="G35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H35">
         <v>-1</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M35">
         <v>-1</v>
@@ -3400,22 +3394,22 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="U35">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y35">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3423,22 +3417,22 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C36">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="D36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F36">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G36">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="H36">
         <v>-1</v>
@@ -3447,13 +3441,13 @@
         <v>-1</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3477,22 +3471,22 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>-1</v>
       </c>
       <c r="V36">
         <v>6</v>
       </c>
       <c r="W36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y36">
-        <v>7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3500,37 +3494,37 @@
         <v>45</v>
       </c>
       <c r="B37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D37">
         <v>7</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F37">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H37">
         <v>-1</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M37">
         <v>-1</v>
@@ -3554,22 +3548,22 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V37">
         <v>7</v>
       </c>
       <c r="W37">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X37">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Y37">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3580,16 +3574,16 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="D38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38">
         <v>7</v>
       </c>
       <c r="F38">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G38">
         <v>6</v>
@@ -3601,13 +3595,13 @@
         <v>-1</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M38">
         <v>-1</v>
@@ -3634,10 +3628,10 @@
         <v>6</v>
       </c>
       <c r="U38">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="V38">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="W38">
         <v>7</v>
@@ -3646,83 +3640,6 @@
         <v>7</v>
       </c>
       <c r="Y38">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39">
-        <v>6</v>
-      </c>
-      <c r="C39">
-        <v>-1</v>
-      </c>
-      <c r="D39">
-        <v>6</v>
-      </c>
-      <c r="E39">
-        <v>7</v>
-      </c>
-      <c r="F39">
-        <v>6</v>
-      </c>
-      <c r="G39">
-        <v>6</v>
-      </c>
-      <c r="H39">
-        <v>-1</v>
-      </c>
-      <c r="I39">
-        <v>-1</v>
-      </c>
-      <c r="J39">
-        <v>-1</v>
-      </c>
-      <c r="K39">
-        <v>-1</v>
-      </c>
-      <c r="L39">
-        <v>-1</v>
-      </c>
-      <c r="M39">
-        <v>-1</v>
-      </c>
-      <c r="N39">
-        <v>-1</v>
-      </c>
-      <c r="O39">
-        <v>-1</v>
-      </c>
-      <c r="P39">
-        <v>-1</v>
-      </c>
-      <c r="Q39">
-        <v>-1</v>
-      </c>
-      <c r="R39">
-        <v>-1</v>
-      </c>
-      <c r="S39">
-        <v>-1</v>
-      </c>
-      <c r="T39">
-        <v>6</v>
-      </c>
-      <c r="U39">
-        <v>-1</v>
-      </c>
-      <c r="V39">
-        <v>6</v>
-      </c>
-      <c r="W39">
-        <v>7</v>
-      </c>
-      <c r="X39">
-        <v>6</v>
-      </c>
-      <c r="Y39">
         <v>6</v>
       </c>
     </row>
@@ -3750,31 +3667,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -3782,25 +3699,25 @@
         <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C2">
         <v>36</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
-        <v>63.89</v>
+        <v>58.33</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <v>13</v>
@@ -3814,7 +3731,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3">
         <v>36</v>
@@ -3843,106 +3760,106 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C4">
         <v>36</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E4">
+        <v>6</v>
+      </c>
+      <c r="F4">
+        <v>83.33</v>
+      </c>
+      <c r="G4">
+        <v>16.67</v>
+      </c>
+      <c r="H4">
+        <v>6.6</v>
+      </c>
+      <c r="I4">
         <v>0</v>
       </c>
-      <c r="F4">
-        <v>86.11</v>
-      </c>
-      <c r="G4">
+      <c r="J4">
         <v>0</v>
-      </c>
-      <c r="H4">
-        <v>7</v>
-      </c>
-      <c r="I4">
-        <v>5</v>
-      </c>
-      <c r="J4">
-        <v>13.89</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C5">
         <v>36</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>91.67</v>
+        <v>86.11</v>
       </c>
       <c r="G5">
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="I5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J5">
-        <v>8.33</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C6">
         <v>36</v>
       </c>
       <c r="D6">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6">
+        <v>88.89</v>
+      </c>
+      <c r="G6">
+        <v>11.11</v>
+      </c>
+      <c r="H6">
+        <v>7.6</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>97.22</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>6.7</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>2.78</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C7">
         <v>36</v>
@@ -3951,22 +3868,22 @@
         <v>35</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>97.22</v>
       </c>
       <c r="G7">
+        <v>2.78</v>
+      </c>
+      <c r="H7">
+        <v>8</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="H7">
-        <v>7.5</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
       <c r="J7">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3976,7 +3893,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3985,16 +3902,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -4008,19 +3925,19 @@
         <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -4028,19 +3945,19 @@
         <v>22330051920289</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -4048,13 +3965,13 @@
         <v>22330051920289</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -4068,19 +3985,19 @@
         <v>22330051920293</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4088,19 +4005,19 @@
         <v>22330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4108,13 +4025,13 @@
         <v>22330051920302</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -4128,44 +4045,44 @@
         <v>22330051920303</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>22330051920303</v>
+        <v>22330051920417</v>
       </c>
       <c r="B9" t="s">
         <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>22330051920417</v>
+        <v>22330051920307</v>
       </c>
       <c r="B10" t="s">
         <v>73</v>
@@ -4174,18 +4091,18 @@
         <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B11" t="s">
         <v>74</v>
@@ -4194,18 +4111,18 @@
         <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>22330051920419</v>
+        <v>22330051920309</v>
       </c>
       <c r="B12" t="s">
         <v>75</v>
@@ -4214,110 +4131,107 @@
         <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B13" t="s">
         <v>76</v>
       </c>
-      <c r="C13" t="s">
-        <v>91</v>
-      </c>
       <c r="D13" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E13" t="s">
         <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>22330051920311</v>
+        <v>22330051920312</v>
       </c>
       <c r="B14" t="s">
         <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>22330051920312</v>
+        <v>22330051920370</v>
       </c>
       <c r="B15" t="s">
         <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>93</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E15" t="s">
         <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16">
-        <v>22330051920370</v>
+        <v>22330051920418</v>
       </c>
       <c r="B16" t="s">
         <v>79</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17">
-        <v>22330051920370</v>
+        <v>22330051920397</v>
       </c>
       <c r="B17" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
         <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>57</v>
@@ -4325,33 +4239,33 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18">
-        <v>22330051920418</v>
+        <v>22330051920373</v>
       </c>
       <c r="B18" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D18" t="s">
         <v>110</v>
       </c>
       <c r="E18" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19">
-        <v>22330051920418</v>
+        <v>22330051920373</v>
       </c>
       <c r="B19" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
         <v>110</v>
@@ -4365,122 +4279,22 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20">
-        <v>22330051920418</v>
+        <v>22330051920315</v>
       </c>
       <c r="B20" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
         <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920397</v>
-      </c>
-      <c r="B21" t="s">
-        <v>81</v>
-      </c>
-      <c r="C21" t="s">
-        <v>79</v>
-      </c>
-      <c r="D21" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920397</v>
-      </c>
-      <c r="B22" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E22" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920373</v>
-      </c>
-      <c r="B23" t="s">
-        <v>82</v>
-      </c>
-      <c r="C23" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" t="s">
-        <v>112</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920373</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920315</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>96</v>
-      </c>
-      <c r="D25" t="s">
-        <v>113</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4499,50 +4313,50 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920418</v>
+        <v>22330051920289</v>
       </c>
       <c r="B2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920289</v>
+        <v>22330051920373</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4550,84 +4364,84 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920303</v>
+        <v>22330051920290</v>
       </c>
       <c r="B4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>22330051920370</v>
+        <v>22330051920293</v>
       </c>
       <c r="B5" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920397</v>
+        <v>22330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="D6" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920373</v>
+        <v>22330051920302</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D7" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920290</v>
+        <v>22330051920303</v>
       </c>
       <c r="B8" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
         <v>84</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4635,16 +4449,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920293</v>
+        <v>22330051920417</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4652,16 +4466,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920297</v>
+        <v>22330051920307</v>
       </c>
       <c r="B10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4669,16 +4483,16 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920302</v>
+        <v>22330051920419</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -4686,16 +4500,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920417</v>
+        <v>22330051920309</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E12">
         <v>1</v>
@@ -4703,16 +4517,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920307</v>
+        <v>22330051920311</v>
       </c>
       <c r="B13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E13">
         <v>1</v>
@@ -4720,16 +4531,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920419</v>
+        <v>22330051920312</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -4737,16 +4548,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920309</v>
+        <v>22330051920370</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E15">
         <v>1</v>
@@ -4754,16 +4565,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920311</v>
+        <v>22330051920418</v>
       </c>
       <c r="B16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
         <v>92</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -4771,16 +4582,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B17" t="s">
+        <v>80</v>
+      </c>
+      <c r="C17" t="s">
         <v>78</v>
       </c>
-      <c r="C17" t="s">
-        <v>93</v>
-      </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E17">
         <v>1</v>
@@ -4791,13 +4602,13 @@
         <v>22330051920315</v>
       </c>
       <c r="B18" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E18">
         <v>1</v>
@@ -4808,13 +4619,13 @@
         <v>22330051920291</v>
       </c>
       <c r="B19" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4825,13 +4636,13 @@
         <v>22330051920294</v>
       </c>
       <c r="B20" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D20" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4842,13 +4653,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C21" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D21" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4859,13 +4670,13 @@
         <v>22330051920295</v>
       </c>
       <c r="B22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4876,13 +4687,13 @@
         <v>22330051920360</v>
       </c>
       <c r="B23" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D23" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4893,13 +4704,13 @@
         <v>22330051920415</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4910,13 +4721,13 @@
         <v>22330051920298</v>
       </c>
       <c r="B25" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C25" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D25" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4927,13 +4738,13 @@
         <v>22330051920300</v>
       </c>
       <c r="B26" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C26" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D26" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4944,13 +4755,13 @@
         <v>22330051920299</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D27" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4961,13 +4772,13 @@
         <v>22330051920301</v>
       </c>
       <c r="B28" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D28" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4978,13 +4789,13 @@
         <v>22330051920304</v>
       </c>
       <c r="B29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4995,13 +4806,13 @@
         <v>22330051920305</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D30" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -5012,13 +4823,13 @@
         <v>22330051920306</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C31" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D31" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -5029,13 +4840,13 @@
         <v>22330051920308</v>
       </c>
       <c r="B32" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D32" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -5046,13 +4857,13 @@
         <v>22330051920310</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C33" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="D33" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -5063,13 +4874,13 @@
         <v>22330051920364</v>
       </c>
       <c r="B34" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C34" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D34" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -5080,13 +4891,13 @@
         <v>22330051920313</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="D35" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -5097,13 +4908,13 @@
         <v>22330051920408</v>
       </c>
       <c r="B36" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D36" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -5114,13 +4925,13 @@
         <v>22330051920314</v>
       </c>
       <c r="B37" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C37" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D37" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -5133,7 +4944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5142,22 +4953,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>4</v>
@@ -5168,19 +4979,19 @@
         <v>22330051920303</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D2" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>-1</v>
@@ -5191,85 +5002,85 @@
         <v>22330051920303</v>
       </c>
       <c r="B3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
         <v>60</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920417</v>
+        <v>22330051920312</v>
       </c>
       <c r="B4" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920417</v>
+        <v>22330051920312</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920370</v>
+        <v>22330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
         <v>109</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>57</v>
@@ -5280,45 +5091,45 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920370</v>
+        <v>22330051920397</v>
       </c>
       <c r="B7" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
         <v>109</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920315</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
         <v>111</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5326,25 +5137,25 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920397</v>
+        <v>22330051920315</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" t="s">
-        <v>79</v>
+        <v>94</v>
       </c>
       <c r="D9" t="s">
         <v>111</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5352,19 +5163,19 @@
         <v>22330051920290</v>
       </c>
       <c r="B10" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>-1</v>
@@ -5375,19 +5186,19 @@
         <v>22330051920291</v>
       </c>
       <c r="B11" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D11" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E11" t="s">
         <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5398,19 +5209,19 @@
         <v>22330051920293</v>
       </c>
       <c r="B12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C12" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>-1</v>
@@ -5418,22 +5229,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920295</v>
+        <v>22330051920412</v>
       </c>
       <c r="B13" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C13" t="s">
-        <v>82</v>
+        <v>124</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -5441,45 +5252,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920297</v>
+        <v>22330051920295</v>
       </c>
       <c r="B14" t="s">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="C14" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>100</v>
+        <v>136</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>57</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920298</v>
+        <v>22330051920360</v>
       </c>
       <c r="B15" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D15" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5487,22 +5298,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920302</v>
+        <v>22330051920297</v>
       </c>
       <c r="B16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C16" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D16" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>-1</v>
@@ -5510,45 +5321,45 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920307</v>
+        <v>22330051920298</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
+        <v>117</v>
       </c>
       <c r="C17" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="D17" t="s">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>57</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920419</v>
+        <v>22330051920302</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="C18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G18">
         <v>-1</v>
@@ -5556,22 +5367,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920309</v>
+        <v>22330051920307</v>
       </c>
       <c r="B19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D19" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G19">
         <v>-1</v>
@@ -5579,22 +5390,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920311</v>
+        <v>22330051920419</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -5602,22 +5413,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920312</v>
+        <v>22330051920309</v>
       </c>
       <c r="B21" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21">
         <v>-1</v>
@@ -5625,22 +5436,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920408</v>
+        <v>22330051920308</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C22" t="s">
-        <v>133</v>
+        <v>71</v>
       </c>
       <c r="D22" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="E22" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G22">
         <v>5</v>
@@ -5648,25 +5459,45 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920315</v>
+        <v>22330051920311</v>
       </c>
       <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="D23" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
       </c>
       <c r="F23" t="s">
+        <v>56</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920408</v>
+      </c>
+      <c r="B24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C24" t="s">
+        <v>131</v>
+      </c>
+      <c r="D24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" t="s">
         <v>57</v>
       </c>
-      <c r="G23">
-        <v>-1</v>
+      <c r="G24">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="420" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -1063,7 +1063,7 @@
         <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1140,7 +1140,7 @@
         <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1217,7 +1217,7 @@
         <v>9</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1253,7 +1253,7 @@
         <v>8</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1294,7 +1294,7 @@
         <v>8</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1371,7 +1371,7 @@
         <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1407,7 +1407,7 @@
         <v>5</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1448,7 +1448,7 @@
         <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1484,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1525,7 +1525,7 @@
         <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1602,7 +1602,7 @@
         <v>8</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1638,7 +1638,7 @@
         <v>9</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1679,7 +1679,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1756,7 +1756,7 @@
         <v>10</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1792,7 +1792,7 @@
         <v>10</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1833,7 +1833,7 @@
         <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1869,7 +1869,7 @@
         <v>6</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1910,7 +1910,7 @@
         <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1987,7 +1987,7 @@
         <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2141,7 +2141,7 @@
         <v>5</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2218,7 +2218,7 @@
         <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2254,7 +2254,7 @@
         <v>9</v>
       </c>
       <c r="Y20">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2295,7 +2295,7 @@
         <v>9</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2449,7 +2449,7 @@
         <v>5</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2485,7 +2485,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2526,7 +2526,7 @@
         <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2603,7 +2603,7 @@
         <v>6</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2680,7 +2680,7 @@
         <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2757,7 +2757,7 @@
         <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2834,7 +2834,7 @@
         <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2870,7 +2870,7 @@
         <v>9</v>
       </c>
       <c r="Y28">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2911,7 +2911,7 @@
         <v>5</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2947,7 +2947,7 @@
         <v>5</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2988,7 +2988,7 @@
         <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3065,7 +3065,7 @@
         <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3101,7 +3101,7 @@
         <v>7</v>
       </c>
       <c r="Y31">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3142,7 +3142,7 @@
         <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3178,7 +3178,7 @@
         <v>7</v>
       </c>
       <c r="Y32">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3219,7 +3219,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3255,7 +3255,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3373,7 +3373,7 @@
         <v>7</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3527,7 +3527,7 @@
         <v>5</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3563,7 +3563,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3604,7 +3604,7 @@
         <v>7</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3801,19 +3801,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>86.11</v>
+        <v>83.33</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>5</v>
@@ -4944,7 +4944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5500,6 +5500,29 @@
         <v>5</v>
       </c>
     </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>22330051920314</v>
+      </c>
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" t="s">
+        <v>132</v>
+      </c>
+      <c r="D25" t="s">
+        <v>149</v>
+      </c>
+      <c r="E25" t="s">
+        <v>10</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -1128,7 +1128,7 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>5</v>
@@ -1164,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1898,7 +1898,7 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1934,7 +1934,7 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -2052,7 +2052,7 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2088,7 +2088,7 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>6</v>
@@ -2976,7 +2976,7 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J30">
         <v>7</v>
@@ -3012,7 +3012,7 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -3705,19 +3705,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>58.33</v>
+        <v>52.78</v>
       </c>
       <c r="G2">
-        <v>5.56</v>
+        <v>11.11</v>
       </c>
       <c r="H2">
-        <v>7</v>
+        <v>6.7</v>
       </c>
       <c r="I2">
         <v>13</v>
@@ -4944,7 +4944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4976,45 +4976,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920303</v>
+        <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920303</v>
+        <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>123</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5022,16 +5022,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920312</v>
+        <v>22330051920303</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D4" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -5045,16 +5045,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920312</v>
+        <v>22330051920303</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5068,22 +5068,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920397</v>
+        <v>22330051920312</v>
       </c>
       <c r="B6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>-1</v>
@@ -5091,22 +5091,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920397</v>
+        <v>22330051920312</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D7" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -5114,22 +5114,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920315</v>
+        <v>22330051920397</v>
       </c>
       <c r="B8" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -5137,16 +5137,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920315</v>
+        <v>22330051920397</v>
       </c>
       <c r="B9" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C9" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -5160,16 +5160,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920290</v>
+        <v>22330051920315</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -5183,22 +5183,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920291</v>
+        <v>22330051920315</v>
       </c>
       <c r="B11" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -5206,16 +5206,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920293</v>
+        <v>22330051920290</v>
       </c>
       <c r="B12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D12" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -5229,45 +5229,45 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920412</v>
+        <v>22330051920293</v>
       </c>
       <c r="B13" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
-        <v>135</v>
+        <v>97</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G13">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920295</v>
+        <v>22330051920412</v>
       </c>
       <c r="B14" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>124</v>
       </c>
       <c r="D14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -5275,22 +5275,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920360</v>
+        <v>22330051920295</v>
       </c>
       <c r="B15" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>125</v>
+        <v>81</v>
       </c>
       <c r="D15" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5298,16 +5298,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920297</v>
+        <v>22330051920360</v>
       </c>
       <c r="B16" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="C16" t="s">
-        <v>86</v>
+        <v>125</v>
       </c>
       <c r="D16" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -5316,67 +5316,67 @@
         <v>56</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920298</v>
+        <v>22330051920297</v>
       </c>
       <c r="B17" t="s">
-        <v>117</v>
+        <v>69</v>
       </c>
       <c r="C17" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="E17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G17">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920302</v>
+        <v>22330051920298</v>
       </c>
       <c r="B18" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="C18" t="s">
-        <v>87</v>
+        <v>126</v>
       </c>
       <c r="D18" t="s">
-        <v>99</v>
+        <v>139</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920307</v>
+        <v>22330051920300</v>
       </c>
       <c r="B19" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C19" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="D19" t="s">
-        <v>102</v>
+        <v>140</v>
       </c>
       <c r="E19" t="s">
         <v>6</v>
@@ -5385,27 +5385,27 @@
         <v>56</v>
       </c>
       <c r="G19">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920419</v>
+        <v>22330051920302</v>
       </c>
       <c r="B20" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -5413,16 +5413,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920309</v>
+        <v>22330051920307</v>
       </c>
       <c r="B21" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D21" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E21" t="s">
         <v>6</v>
@@ -5436,36 +5436,39 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920308</v>
+        <v>22330051920419</v>
       </c>
       <c r="B22" t="s">
-        <v>118</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="D22" t="s">
-        <v>79</v>
+        <v>103</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G22">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920311</v>
+        <v>22330051920309</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="C23" t="s">
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -5479,22 +5482,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920408</v>
+        <v>22330051920308</v>
       </c>
       <c r="B24" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="C24" t="s">
-        <v>131</v>
+        <v>71</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>79</v>
       </c>
       <c r="E24" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -5502,24 +5505,67 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
+        <v>22330051920311</v>
+      </c>
+      <c r="B25" t="s">
+        <v>76</v>
+      </c>
+      <c r="D25" t="s">
+        <v>105</v>
+      </c>
+      <c r="E25" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" t="s">
+        <v>56</v>
+      </c>
+      <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>22330051920408</v>
+      </c>
+      <c r="B26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>131</v>
+      </c>
+      <c r="D26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E26" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
         <v>22330051920314</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B27" t="s">
         <v>122</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C27" t="s">
         <v>132</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D27" t="s">
         <v>149</v>
       </c>
-      <c r="E25" t="s">
+      <c r="E27" t="s">
         <v>10</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F27" t="s">
         <v>59</v>
       </c>
-      <c r="G25">
+      <c r="G27">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -971,7 +971,7 @@
         <v>-1</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1048,7 +1048,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1125,7 +1125,7 @@
         <v>6</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -1202,7 +1202,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U7">
         <v>-1</v>
@@ -1279,7 +1279,7 @@
         <v>7</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I8">
         <v>6</v>
@@ -1356,7 +1356,7 @@
         <v>9</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I9">
         <v>6</v>
@@ -1392,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1433,7 +1433,7 @@
         <v>7</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>5</v>
@@ -1469,7 +1469,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1510,13 +1510,13 @@
         <v>7</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
         <v>10</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K11">
         <v>8</v>
@@ -1546,13 +1546,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1587,7 +1587,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1664,7 +1664,7 @@
         <v>6</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>6</v>
@@ -1676,7 +1676,7 @@
         <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>6</v>
@@ -1741,7 +1741,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I14">
         <v>6</v>
@@ -1777,7 +1777,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U14">
         <v>6</v>
@@ -1818,7 +1818,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>6</v>
@@ -1895,7 +1895,7 @@
         <v>8</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I16">
         <v>5</v>
@@ -1931,7 +1931,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1972,7 +1972,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>7</v>
@@ -2049,7 +2049,7 @@
         <v>-1</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I18">
         <v>5</v>
@@ -2085,7 +2085,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U18">
         <v>6</v>
@@ -2126,13 +2126,13 @@
         <v>7</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K19">
         <v>8</v>
@@ -2168,7 +2168,7 @@
         <v>-1</v>
       </c>
       <c r="V19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W19">
         <v>7</v>
@@ -2203,7 +2203,7 @@
         <v>6</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I20">
         <v>6</v>
@@ -2280,13 +2280,13 @@
         <v>6</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>6</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K21">
         <v>8</v>
@@ -2316,13 +2316,13 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>6</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2357,7 +2357,7 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>5</v>
@@ -2434,7 +2434,7 @@
         <v>6</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I23">
         <v>6</v>
@@ -2470,7 +2470,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
         <v>6</v>
@@ -2511,7 +2511,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>-1</v>
@@ -2588,7 +2588,7 @@
         <v>7</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>-1</v>
@@ -2665,7 +2665,7 @@
         <v>7</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I26">
         <v>6</v>
@@ -2701,7 +2701,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2742,7 +2742,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2819,7 +2819,7 @@
         <v>8</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U28">
         <v>8</v>
@@ -2896,7 +2896,7 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2973,7 +2973,7 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>5</v>
@@ -3009,7 +3009,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -3050,7 +3050,7 @@
         <v>6</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I31">
         <v>6</v>
@@ -3127,7 +3127,7 @@
         <v>8</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3163,7 +3163,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U32">
         <v>-1</v>
@@ -3204,7 +3204,7 @@
         <v>6</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I33">
         <v>10</v>
@@ -3216,7 +3216,7 @@
         <v>8</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -3281,7 +3281,7 @@
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I34">
         <v>10</v>
@@ -3435,7 +3435,7 @@
         <v>-1</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3512,7 +3512,7 @@
         <v>6</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I37">
         <v>6</v>
@@ -3548,7 +3548,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3589,7 +3589,7 @@
         <v>6</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3625,7 +3625,7 @@
         <v>-1</v>
       </c>
       <c r="T38">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U38">
         <v>-1</v>
@@ -3737,19 +3737,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>75</v>
+        <v>61.11</v>
       </c>
       <c r="G3">
-        <v>22.22</v>
+        <v>36.11</v>
       </c>
       <c r="H3">
-        <v>6.1</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>1</v>
@@ -4944,7 +4944,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5022,39 +5022,39 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920303</v>
+        <v>22330051920412</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920303</v>
+        <v>22330051920412</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5068,16 +5068,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920312</v>
+        <v>22330051920303</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -5091,16 +5091,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920312</v>
+        <v>22330051920303</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="D7" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5114,16 +5114,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -5132,165 +5132,165 @@
         <v>57</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920397</v>
+        <v>22330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G9">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920315</v>
+        <v>22330051920419</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920315</v>
+        <v>22330051920419</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C11" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G11">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920290</v>
+        <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>66</v>
+        <v>118</v>
       </c>
       <c r="C12" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>79</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920293</v>
+        <v>22330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>71</v>
       </c>
       <c r="D13" t="s">
-        <v>97</v>
+        <v>79</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920412</v>
+        <v>22330051920312</v>
       </c>
       <c r="B14" t="s">
-        <v>114</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G14">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920295</v>
+        <v>22330051920312</v>
       </c>
       <c r="B15" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5298,62 +5298,62 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920360</v>
+        <v>22330051920397</v>
       </c>
       <c r="B16" t="s">
-        <v>115</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>125</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16">
-        <v>5</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920297</v>
+        <v>22330051920397</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="E17" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920298</v>
+        <v>22330051920314</v>
       </c>
       <c r="B18" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="D18" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -5367,22 +5367,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920300</v>
+        <v>22330051920314</v>
       </c>
       <c r="B19" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="C19" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="D19" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -5390,22 +5390,22 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920302</v>
+        <v>22330051920315</v>
       </c>
       <c r="B20" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>99</v>
+        <v>111</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G20">
         <v>-1</v>
@@ -5413,39 +5413,39 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920307</v>
+        <v>22330051920315</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C21" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="D21" t="s">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920419</v>
+        <v>22330051920290</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C22" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -5459,16 +5459,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920309</v>
+        <v>22330051920293</v>
       </c>
       <c r="B23" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C23" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D23" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E23" t="s">
         <v>6</v>
@@ -5482,22 +5482,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920308</v>
+        <v>22330051920360</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C24" t="s">
-        <v>71</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -5505,13 +5505,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920311</v>
+        <v>22330051920297</v>
       </c>
       <c r="B25" t="s">
-        <v>76</v>
+        <v>69</v>
+      </c>
+      <c r="C25" t="s">
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -5525,16 +5528,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920408</v>
+        <v>22330051920298</v>
       </c>
       <c r="B26" t="s">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="C26" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>103</v>
+        <v>139</v>
       </c>
       <c r="E26" t="s">
         <v>5</v>
@@ -5548,24 +5551,113 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920314</v>
+        <v>22330051920300</v>
       </c>
       <c r="B27" t="s">
-        <v>122</v>
+        <v>70</v>
       </c>
       <c r="C27" t="s">
-        <v>132</v>
+        <v>92</v>
       </c>
       <c r="D27" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="E27" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>22330051920302</v>
+      </c>
+      <c r="B28" t="s">
+        <v>70</v>
+      </c>
+      <c r="C28" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" t="s">
+        <v>99</v>
+      </c>
+      <c r="E28" t="s">
         <v>10</v>
       </c>
-      <c r="F27" t="s">
+      <c r="F28" t="s">
         <v>59</v>
       </c>
-      <c r="G27">
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>22330051920309</v>
+      </c>
+      <c r="B29" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" t="s">
+        <v>6</v>
+      </c>
+      <c r="F29" t="s">
+        <v>56</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>22330051920311</v>
+      </c>
+      <c r="B30" t="s">
+        <v>76</v>
+      </c>
+      <c r="D30" t="s">
+        <v>105</v>
+      </c>
+      <c r="E30" t="s">
+        <v>6</v>
+      </c>
+      <c r="F30" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>22330051920408</v>
+      </c>
+      <c r="B31" t="s">
+        <v>87</v>
+      </c>
+      <c r="C31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D31" t="s">
+        <v>103</v>
+      </c>
+      <c r="E31" t="s">
+        <v>5</v>
+      </c>
+      <c r="F31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -188,12 +188,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>Medina Tolentino Francisco</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -224,12 +224,33 @@
     <t>ARIAS</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
     <t>CANTE</t>
   </si>
   <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>CONDE</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
+    <t>ESPARZA</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -239,6 +260,9 @@
     <t>LIBRADO</t>
   </si>
   <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -248,12 +272,24 @@
     <t>PARRA</t>
   </si>
   <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PUGA CABRERA</t>
   </si>
   <si>
     <t>QUESADA</t>
   </si>
   <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -263,45 +299,72 @@
     <t>SANTOS</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
     <t>VENTURA</t>
   </si>
   <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>CORTES</t>
+    <t>ALVAREZ</t>
   </si>
   <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>VALDEZ</t>
+  </si>
+  <si>
     <t>CARBAJAL</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>FLORES</t>
   </si>
   <si>
     <t>MAYAHUA</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>ISLAS</t>
   </si>
   <si>
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>LOPEZ</t>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>MARIN</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
   </si>
   <si>
     <t>LUIS</t>
   </si>
   <si>
+    <t>PAZ</t>
+  </si>
+  <si>
     <t>TEZOCO</t>
   </si>
   <si>
@@ -311,21 +374,60 @@
     <t>JESUS YEHUDIEL</t>
   </si>
   <si>
+    <t>EFRAIN DE JESUS</t>
+  </si>
+  <si>
     <t>TOMAS RAFAEL</t>
   </si>
   <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>GAEL</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>PABLO</t>
   </si>
   <si>
+    <t>CELINA MONSERRAT</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ISAI</t>
+  </si>
+  <si>
+    <t>TONALLI</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
     <t>ABDIEL ARMANDO</t>
   </si>
   <si>
     <t>ANGEL DE JESUS</t>
   </si>
   <si>
+    <t>AARON</t>
+  </si>
+  <si>
+    <t>GAMALIEL</t>
+  </si>
+  <si>
     <t>LESLIE YAMILET</t>
   </si>
   <si>
+    <t>JOSE MARCELO</t>
+  </si>
+  <si>
     <t>JOSUE ISRAEL</t>
   </si>
   <si>
@@ -335,12 +437,21 @@
     <t>MOISES ALBERTO</t>
   </si>
   <si>
+    <t>ANA LAURA</t>
+  </si>
+  <si>
     <t>ALEJANDRO</t>
   </si>
   <si>
     <t>JARED DE JESUS</t>
   </si>
   <si>
+    <t>ESTEPHANY</t>
+  </si>
+  <si>
+    <t>ULISES HIRAM</t>
+  </si>
+  <si>
     <t>MIRIAM AIMAR</t>
   </si>
   <si>
@@ -353,121 +464,10 @@
     <t>ANGEL FRANCISCO</t>
   </si>
   <si>
+    <t>GUILLERMO ALEXANDER</t>
+  </si>
+  <si>
     <t>ZABDIEL</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CONDE</t>
-  </si>
-  <si>
-    <t>ESPARZA</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>VALDEZ</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>ISLAS</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MARIN</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>PAZ</t>
-  </si>
-  <si>
-    <t>EFRAIN DE JESUS</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>GAEL</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>CELINA MONSERRAT</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ISAI</t>
-  </si>
-  <si>
-    <t>TONALLI</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>AARON</t>
-  </si>
-  <si>
-    <t>GAMALIEL</t>
-  </si>
-  <si>
-    <t>JOSE MARCELO</t>
-  </si>
-  <si>
-    <t>ANA LAURA</t>
-  </si>
-  <si>
-    <t>ESTEPHANY</t>
-  </si>
-  <si>
-    <t>ULISES HIRAM</t>
-  </si>
-  <si>
-    <t>GUILLERMO ALEXANDER</t>
   </si>
 </sst>
 </file>
@@ -956,7 +956,7 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D4">
         <v>6</v>
@@ -968,13 +968,13 @@
         <v>8</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>5</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J4">
         <v>4</v>
@@ -986,7 +986,7 @@
         <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1010,7 +1010,7 @@
         <v>5</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
@@ -1022,7 +1022,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1033,7 +1033,7 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D5">
         <v>7</v>
@@ -1051,7 +1051,7 @@
         <v>6</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J5">
         <v>9</v>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V5">
         <v>8</v>
@@ -1187,7 +1187,7 @@
         <v>6</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>7</v>
@@ -1205,7 +1205,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
         <v>10</v>
@@ -1241,7 +1241,7 @@
         <v>8</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
         <v>9</v>
@@ -1572,7 +1572,7 @@
         <v>6</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
         <v>6</v>
@@ -1590,7 +1590,7 @@
         <v>6</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1626,7 +1626,7 @@
         <v>6</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
         <v>6</v>
@@ -2046,7 +2046,7 @@
         <v>6</v>
       </c>
       <c r="G18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H18">
         <v>7</v>
@@ -2064,7 +2064,7 @@
         <v>6</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2100,7 +2100,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2111,7 +2111,7 @@
         <v>7</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D19">
         <v>7</v>
@@ -2129,7 +2129,7 @@
         <v>6</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>5</v>
@@ -2165,7 +2165,7 @@
         <v>7</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V19">
         <v>6</v>
@@ -2354,7 +2354,7 @@
         <v>7</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H22">
         <v>5</v>
@@ -2372,7 +2372,7 @@
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2408,7 +2408,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2496,7 +2496,7 @@
         <v>6</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
         <v>6</v>
@@ -2514,7 +2514,7 @@
         <v>5</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
         <v>7</v>
@@ -2550,7 +2550,7 @@
         <v>5</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
         <v>7</v>
@@ -2573,7 +2573,7 @@
         <v>6</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
         <v>6</v>
@@ -2591,7 +2591,7 @@
         <v>5</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
         <v>7</v>
@@ -2627,7 +2627,7 @@
         <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
         <v>7</v>
@@ -2727,7 +2727,7 @@
         <v>7</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D27">
         <v>6</v>
@@ -2745,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2781,7 +2781,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2881,7 +2881,7 @@
         <v>6</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
         <v>7</v>
@@ -2899,7 +2899,7 @@
         <v>6</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J29">
         <v>7</v>
@@ -2935,7 +2935,7 @@
         <v>6</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V29">
         <v>7</v>
@@ -3112,7 +3112,7 @@
         <v>6</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D32">
         <v>6</v>
@@ -3130,7 +3130,7 @@
         <v>5</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J32">
         <v>5</v>
@@ -3166,7 +3166,7 @@
         <v>5</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V32">
         <v>5</v>
@@ -3278,7 +3278,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H34">
         <v>5</v>
@@ -3296,7 +3296,7 @@
         <v>8</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3332,7 +3332,7 @@
         <v>7</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3340,7 +3340,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="C35">
         <v>6</v>
@@ -3358,7 +3358,7 @@
         <v>7</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I35">
         <v>6</v>
@@ -3394,7 +3394,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U35">
         <v>6</v>
@@ -3420,7 +3420,7 @@
         <v>5</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D36">
         <v>7</v>
@@ -3432,13 +3432,13 @@
         <v>8</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>6</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -3450,7 +3450,7 @@
         <v>9</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3474,7 +3474,7 @@
         <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>6</v>
@@ -3486,7 +3486,7 @@
         <v>9</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3574,7 +3574,7 @@
         <v>6</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D38">
         <v>6</v>
@@ -3592,7 +3592,7 @@
         <v>7</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
         <v>5</v>
@@ -3628,7 +3628,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3705,30 +3705,30 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>52.78</v>
+        <v>61.11</v>
       </c>
       <c r="G2">
-        <v>11.11</v>
+        <v>38.89</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="I2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>36.11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3740,22 +3740,22 @@
         <v>22</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3">
         <v>61.11</v>
       </c>
       <c r="G3">
-        <v>36.11</v>
+        <v>38.89</v>
       </c>
       <c r="H3">
         <v>6.3</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3801,25 +3801,25 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>83.33</v>
+        <v>88.89</v>
       </c>
       <c r="G5">
-        <v>2.78</v>
+        <v>11.11</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>13.89</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3893,7 +3893,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3918,383 +3918,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920290</v>
-      </c>
-      <c r="B2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920289</v>
-      </c>
-      <c r="B3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920289</v>
-      </c>
-      <c r="B4" t="s">
-        <v>67</v>
-      </c>
-      <c r="C4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920293</v>
-      </c>
-      <c r="B5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920297</v>
-      </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>86</v>
-      </c>
-      <c r="D6" t="s">
-        <v>98</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920302</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>87</v>
-      </c>
-      <c r="D7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920303</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" t="s">
-        <v>100</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920417</v>
-      </c>
-      <c r="B9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C9" t="s">
-        <v>87</v>
-      </c>
-      <c r="D9" t="s">
-        <v>101</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920307</v>
-      </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" t="s">
-        <v>102</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920419</v>
-      </c>
-      <c r="B11" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D11" t="s">
-        <v>103</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920309</v>
-      </c>
-      <c r="B12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C12" t="s">
-        <v>90</v>
-      </c>
-      <c r="D12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920311</v>
-      </c>
-      <c r="B13" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920312</v>
-      </c>
-      <c r="B14" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920370</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D15" t="s">
-        <v>107</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920418</v>
-      </c>
-      <c r="B16" t="s">
-        <v>79</v>
-      </c>
-      <c r="C16" t="s">
-        <v>92</v>
-      </c>
-      <c r="D16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920397</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>78</v>
-      </c>
-      <c r="D17" t="s">
-        <v>109</v>
-      </c>
-      <c r="E17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920373</v>
-      </c>
-      <c r="B18" t="s">
-        <v>81</v>
-      </c>
-      <c r="C18" t="s">
-        <v>93</v>
-      </c>
-      <c r="D18" t="s">
-        <v>110</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920373</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>93</v>
-      </c>
-      <c r="D19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920315</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>94</v>
-      </c>
-      <c r="D20" t="s">
-        <v>111</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -4330,53 +3953,53 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>22330051920289</v>
+        <v>22330051920290</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="D2" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>22330051920373</v>
+        <v>22330051920289</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>22330051920290</v>
+        <v>22330051920291</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="D4" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -4384,245 +4007,248 @@
         <v>22330051920293</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C5" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D5" t="s">
-        <v>97</v>
+        <v>119</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>22330051920297</v>
+        <v>22330051920294</v>
       </c>
       <c r="B6" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C6" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>98</v>
+        <v>120</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>22330051920302</v>
+        <v>22330051920412</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="D7" t="s">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>22330051920303</v>
+        <v>22330051920295</v>
       </c>
       <c r="B8" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C8" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>100</v>
+        <v>122</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>22330051920417</v>
+        <v>22330051920360</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>101</v>
+        <v>123</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>22330051920307</v>
+        <v>22330051920297</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>124</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>22330051920419</v>
+        <v>22330051920415</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>22330051920309</v>
+        <v>22330051920298</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D12" t="s">
-        <v>104</v>
+        <v>126</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>22330051920311</v>
+        <v>22330051920300</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="C13" t="s">
+        <v>80</v>
       </c>
       <c r="D13" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>22330051920312</v>
+        <v>22330051920299</v>
       </c>
       <c r="B14" t="s">
         <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>22330051920370</v>
+        <v>22330051920301</v>
       </c>
       <c r="B15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>71</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>129</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>22330051920418</v>
+        <v>22330051920302</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C16" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D16" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>22330051920397</v>
+        <v>22330051920303</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="E17">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>22330051920315</v>
+        <v>22330051920304</v>
       </c>
       <c r="B18" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="D18" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="E18">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>22330051920291</v>
+        <v>22330051920305</v>
       </c>
       <c r="B19" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4633,13 +4259,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>22330051920294</v>
+        <v>22330051920417</v>
       </c>
       <c r="B20" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4650,13 +4276,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>22330051920412</v>
+        <v>22330051920306</v>
       </c>
       <c r="B21" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4667,13 +4293,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>22330051920295</v>
+        <v>22330051920307</v>
       </c>
       <c r="B22" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4684,13 +4310,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>22330051920360</v>
+        <v>22330051920419</v>
       </c>
       <c r="B23" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4701,13 +4327,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>22330051920415</v>
+        <v>22330051920309</v>
       </c>
       <c r="B24" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4718,16 +4344,16 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>22330051920298</v>
+        <v>22330051920308</v>
       </c>
       <c r="B25" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>126</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>139</v>
+        <v>91</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -4735,16 +4361,16 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>22330051920300</v>
+        <v>22330051920310</v>
       </c>
       <c r="B26" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -4752,16 +4378,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>22330051920299</v>
+        <v>22330051920311</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
-      </c>
-      <c r="C27" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -4769,16 +4392,16 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>22330051920301</v>
+        <v>22330051920312</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="D28" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -4786,16 +4409,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>22330051920304</v>
+        <v>22330051920364</v>
       </c>
       <c r="B29" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>110</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4803,16 +4426,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>22330051920305</v>
+        <v>22330051920313</v>
       </c>
       <c r="B30" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>89</v>
+        <v>111</v>
       </c>
       <c r="D30" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4820,16 +4443,16 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>22330051920306</v>
+        <v>22330051920370</v>
       </c>
       <c r="B31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D31" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -4837,16 +4460,16 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>22330051920308</v>
+        <v>22330051920418</v>
       </c>
       <c r="B32" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>71</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -4854,13 +4477,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>22330051920310</v>
+        <v>22330051920397</v>
       </c>
       <c r="B33" t="s">
-        <v>119</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>128</v>
+        <v>90</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4871,16 +4494,16 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>22330051920364</v>
+        <v>22330051920408</v>
       </c>
       <c r="B34" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>129</v>
+        <v>112</v>
       </c>
       <c r="D34" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -4888,16 +4511,16 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>22330051920313</v>
+        <v>22330051920373</v>
       </c>
       <c r="B35" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
       <c r="C35" t="s">
-        <v>130</v>
+        <v>113</v>
       </c>
       <c r="D35" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -4905,16 +4528,16 @@
     </row>
     <row r="36" spans="1:5">
       <c r="A36">
-        <v>22330051920408</v>
+        <v>22330051920314</v>
       </c>
       <c r="B36" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>148</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -4922,13 +4545,13 @@
     </row>
     <row r="37" spans="1:5">
       <c r="A37">
-        <v>22330051920314</v>
+        <v>22330051920315</v>
       </c>
       <c r="B37" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C37" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D37" t="s">
         <v>149</v>
@@ -4944,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4979,19 +4602,19 @@
         <v>22330051920291</v>
       </c>
       <c r="B2" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D2" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5002,19 +4625,19 @@
         <v>22330051920291</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>123</v>
+        <v>98</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>118</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5025,19 +4648,19 @@
         <v>22330051920412</v>
       </c>
       <c r="B4" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C4" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D4" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -5048,13 +4671,13 @@
         <v>22330051920412</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="E5" t="s">
         <v>9</v>
@@ -5071,22 +4694,22 @@
         <v>22330051920303</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C6" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -5094,13 +4717,13 @@
         <v>22330051920303</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C7" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
@@ -5117,19 +4740,19 @@
         <v>22330051920307</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D8" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -5140,22 +4763,22 @@
         <v>22330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>102</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
         <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -5163,19 +4786,19 @@
         <v>22330051920419</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -5186,22 +4809,22 @@
         <v>22330051920419</v>
       </c>
       <c r="B11" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="D11" t="s">
-        <v>103</v>
+        <v>137</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -5209,19 +4832,19 @@
         <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E12" t="s">
         <v>5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -5232,13 +4855,13 @@
         <v>22330051920308</v>
       </c>
       <c r="B13" t="s">
-        <v>118</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -5252,45 +4875,45 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F14" t="s">
         <v>56</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920312</v>
+        <v>22330051920397</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="C15" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>146</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -5298,45 +4921,45 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920397</v>
+        <v>22330051920314</v>
       </c>
       <c r="B16" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C16" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
         <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920397</v>
+        <v>22330051920314</v>
       </c>
       <c r="B17" t="s">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>148</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F17" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -5344,19 +4967,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920314</v>
+        <v>22330051920315</v>
       </c>
       <c r="B18" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D18" t="s">
         <v>149</v>
       </c>
       <c r="E18" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F18" t="s">
         <v>57</v>
@@ -5367,22 +4990,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920314</v>
+        <v>22330051920315</v>
       </c>
       <c r="B19" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="C19" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="D19" t="s">
         <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F19" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -5390,45 +5013,45 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920315</v>
+        <v>22330051920290</v>
       </c>
       <c r="B20" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
       </c>
       <c r="F20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G20">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920315</v>
+        <v>22330051920360</v>
       </c>
       <c r="B21" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C21" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D21" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="E21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -5436,68 +5059,68 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920290</v>
+        <v>22330051920297</v>
       </c>
       <c r="B22" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="C22" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>124</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
       </c>
       <c r="F22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920293</v>
+        <v>22330051920298</v>
       </c>
       <c r="B23" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C23" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F23" t="s">
         <v>56</v>
       </c>
       <c r="G23">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920360</v>
+        <v>22330051920300</v>
       </c>
       <c r="B24" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="D24" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
         <v>6</v>
       </c>
       <c r="F24" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -5505,42 +5128,39 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920297</v>
+        <v>22330051920309</v>
       </c>
       <c r="B25" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="C25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>98</v>
+        <v>138</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
       </c>
       <c r="F25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G25">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920298</v>
+        <v>22330051920311</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
-      </c>
-      <c r="C26" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="D26" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E26" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F26" t="s">
         <v>57</v>
@@ -5551,22 +5171,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920300</v>
+        <v>22330051920312</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C27" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="D27" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E27" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -5574,90 +5194,47 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920302</v>
+        <v>22330051920408</v>
       </c>
       <c r="B28" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="C28" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
-        <v>99</v>
+        <v>137</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>22330051920309</v>
+        <v>22330051920373</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C29" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="E29" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" t="s">
         <v>56</v>
       </c>
       <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920311</v>
-      </c>
-      <c r="B30" t="s">
-        <v>76</v>
-      </c>
-      <c r="D30" t="s">
-        <v>105</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>56</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920408</v>
-      </c>
-      <c r="B31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C31" t="s">
-        <v>131</v>
-      </c>
-      <c r="D31" t="s">
-        <v>103</v>
-      </c>
-      <c r="E31" t="s">
-        <v>5</v>
-      </c>
-      <c r="F31" t="s">
-        <v>57</v>
-      </c>
-      <c r="G31">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -995,10 +995,10 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -1072,10 +1072,10 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -1090,7 +1090,7 @@
         <v>5</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W5">
         <v>8</v>
@@ -1149,10 +1149,10 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1226,10 +1226,10 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1244,7 +1244,7 @@
         <v>8</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1303,10 +1303,10 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1380,10 +1380,10 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1401,7 +1401,7 @@
         <v>7</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1457,10 +1457,10 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1534,10 +1534,10 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1552,7 +1552,7 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W11">
         <v>9</v>
@@ -1611,10 +1611,10 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1632,7 +1632,7 @@
         <v>6</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>9</v>
@@ -1688,10 +1688,10 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1706,7 +1706,7 @@
         <v>7</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1765,10 +1765,10 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1783,7 +1783,7 @@
         <v>6</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>10</v>
@@ -1842,10 +1842,10 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1898,7 +1898,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>7</v>
@@ -1919,10 +1919,10 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1934,7 +1934,7 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V16">
         <v>7</v>
@@ -1996,10 +1996,10 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -2014,7 +2014,7 @@
         <v>7</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2073,10 +2073,10 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2091,7 +2091,7 @@
         <v>6</v>
       </c>
       <c r="V18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W18">
         <v>8</v>
@@ -2150,10 +2150,10 @@
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -2227,10 +2227,10 @@
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2248,7 +2248,7 @@
         <v>6</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>9</v>
@@ -2304,10 +2304,10 @@
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2381,10 +2381,10 @@
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2458,10 +2458,10 @@
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2535,10 +2535,10 @@
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2553,7 +2553,7 @@
         <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>7</v>
@@ -2612,10 +2612,10 @@
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2689,10 +2689,10 @@
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2707,7 +2707,7 @@
         <v>7</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>7</v>
@@ -2745,7 +2745,7 @@
         <v>6</v>
       </c>
       <c r="I27">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J27">
         <v>7</v>
@@ -2766,10 +2766,10 @@
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2781,7 +2781,7 @@
         <v>7</v>
       </c>
       <c r="U27">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V27">
         <v>7</v>
@@ -2843,10 +2843,10 @@
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2864,7 +2864,7 @@
         <v>7</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X28">
         <v>9</v>
@@ -2920,10 +2920,10 @@
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2938,7 +2938,7 @@
         <v>6</v>
       </c>
       <c r="V29">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -2976,7 +2976,7 @@
         <v>10</v>
       </c>
       <c r="I30">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J30">
         <v>7</v>
@@ -2997,10 +2997,10 @@
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -3012,7 +3012,7 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>7</v>
@@ -3074,10 +3074,10 @@
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -3151,10 +3151,10 @@
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -3172,7 +3172,7 @@
         <v>5</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>7</v>
@@ -3228,10 +3228,10 @@
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3246,10 +3246,10 @@
         <v>9</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X33">
         <v>7</v>
@@ -3305,10 +3305,10 @@
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3382,10 +3382,10 @@
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3403,7 +3403,7 @@
         <v>5</v>
       </c>
       <c r="W35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>7</v>
@@ -3459,10 +3459,10 @@
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3480,7 +3480,7 @@
         <v>6</v>
       </c>
       <c r="W36">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X36">
         <v>9</v>
@@ -3536,10 +3536,10 @@
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3554,7 +3554,7 @@
         <v>7</v>
       </c>
       <c r="V37">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W37">
         <v>8</v>
@@ -3613,10 +3613,10 @@
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3737,19 +3737,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>61.11</v>
+        <v>66.67</v>
       </c>
       <c r="G3">
-        <v>38.89</v>
+        <v>33.33</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3769,19 +3769,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>83.33</v>
+        <v>80.56</v>
       </c>
       <c r="G4">
-        <v>16.67</v>
+        <v>19.44</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3865,16 +3865,16 @@
         <v>36</v>
       </c>
       <c r="D7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>97.22</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="H7">
         <v>8</v>
@@ -4567,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920300</v>
+        <v>22330051920302</v>
       </c>
       <c r="B24" t="s">
         <v>77</v>
       </c>
       <c r="C24" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G24">
         <v>5</v>
@@ -5128,16 +5128,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>22330051920309</v>
+        <v>22330051920311</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E25" t="s">
         <v>6</v>
@@ -5151,19 +5148,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>22330051920311</v>
+        <v>22330051920312</v>
       </c>
       <c r="B26" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="C26" t="s">
+        <v>109</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E26" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G26">
         <v>5</v>
@@ -5171,22 +5171,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>22330051920312</v>
+        <v>22330051920408</v>
       </c>
       <c r="B27" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="C27" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D27" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G27">
         <v>5</v>
@@ -5194,16 +5194,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>22330051920408</v>
+        <v>22330051920373</v>
       </c>
       <c r="B28" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D28" t="s">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="E28" t="s">
         <v>5</v>
@@ -5212,29 +5212,6 @@
         <v>56</v>
       </c>
       <c r="G28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920373</v>
-      </c>
-      <c r="B29" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" t="s">
-        <v>113</v>
-      </c>
-      <c r="D29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>5</v>
-      </c>
-      <c r="F29" t="s">
-        <v>56</v>
-      </c>
-      <c r="G29">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -200,10 +200,10 @@
     <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
+    <t>Contreras Díaz Irma Ivette</t>
+  </si>
+  <si>
     <t>Pesce Bautista Victor Manuel</t>
-  </si>
-  <si>
-    <t>Contreras Díaz Irma Ivette</t>
   </si>
   <si>
     <t>NC</t>
@@ -1001,7 +1001,7 @@
         <v>6</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -1019,7 +1019,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>5</v>
@@ -1078,7 +1078,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -1155,7 +1155,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -1173,7 +1173,7 @@
         <v>8</v>
       </c>
       <c r="X6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y6">
         <v>6</v>
@@ -1232,7 +1232,7 @@
         <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1309,7 +1309,7 @@
         <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1327,7 +1327,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y8">
         <v>7</v>
@@ -1386,7 +1386,7 @@
         <v>10</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1404,7 +1404,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>10</v>
@@ -1463,7 +1463,7 @@
         <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1540,7 +1540,7 @@
         <v>8</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1617,7 +1617,7 @@
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1694,7 +1694,7 @@
         <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>10</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1848,7 +1848,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1866,7 +1866,7 @@
         <v>9</v>
       </c>
       <c r="X15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1925,7 +1925,7 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -2002,7 +2002,7 @@
         <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -2079,7 +2079,7 @@
         <v>8</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2156,7 +2156,7 @@
         <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S19">
         <v>-1</v>
@@ -2174,7 +2174,7 @@
         <v>7</v>
       </c>
       <c r="X19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2233,7 +2233,7 @@
         <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
         <v>-1</v>
@@ -2310,7 +2310,7 @@
         <v>8</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
         <v>-1</v>
@@ -2387,7 +2387,7 @@
         <v>8</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S22">
         <v>-1</v>
@@ -2464,7 +2464,7 @@
         <v>8</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S23">
         <v>-1</v>
@@ -2482,7 +2482,7 @@
         <v>8</v>
       </c>
       <c r="X23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y23">
         <v>8</v>
@@ -2541,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S24">
         <v>-1</v>
@@ -2559,7 +2559,7 @@
         <v>7</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>6</v>
@@ -2618,7 +2618,7 @@
         <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S25">
         <v>-1</v>
@@ -2695,7 +2695,7 @@
         <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S26">
         <v>-1</v>
@@ -2713,7 +2713,7 @@
         <v>7</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>7</v>
@@ -2772,7 +2772,7 @@
         <v>9</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S27">
         <v>-1</v>
@@ -2790,7 +2790,7 @@
         <v>9</v>
       </c>
       <c r="X27">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2849,7 +2849,7 @@
         <v>8</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
         <v>-1</v>
@@ -2926,7 +2926,7 @@
         <v>8</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
         <v>-1</v>
@@ -2944,7 +2944,7 @@
         <v>9</v>
       </c>
       <c r="X29">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y29">
         <v>8</v>
@@ -3003,7 +3003,7 @@
         <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
         <v>-1</v>
@@ -3080,7 +3080,7 @@
         <v>8</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
         <v>-1</v>
@@ -3098,7 +3098,7 @@
         <v>8</v>
       </c>
       <c r="X31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>8</v>
@@ -3157,7 +3157,7 @@
         <v>8</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
         <v>-1</v>
@@ -3234,7 +3234,7 @@
         <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S33">
         <v>-1</v>
@@ -3311,7 +3311,7 @@
         <v>7</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S34">
         <v>-1</v>
@@ -3388,7 +3388,7 @@
         <v>8</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S35">
         <v>-1</v>
@@ -3465,7 +3465,7 @@
         <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S36">
         <v>-1</v>
@@ -3542,7 +3542,7 @@
         <v>9</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>-1</v>
@@ -3619,7 +3619,7 @@
         <v>7</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S38">
         <v>-1</v>
@@ -3824,7 +3824,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>60</v>
@@ -3833,19 +3833,19 @@
         <v>36</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>88.89</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -3856,7 +3856,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -3877,7 +3877,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4567,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4645,16 +4645,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920412</v>
+        <v>22330051920307</v>
       </c>
       <c r="B4" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D4" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920412</v>
+        <v>22330051920307</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="D5" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4691,22 +4691,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920303</v>
+        <v>22330051920419</v>
       </c>
       <c r="B6" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4714,22 +4714,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920303</v>
+        <v>22330051920419</v>
       </c>
       <c r="B7" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
       <c r="D7" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4737,16 +4737,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920307</v>
+        <v>22330051920397</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4760,22 +4760,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920307</v>
+        <v>22330051920397</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4783,16 +4783,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920419</v>
+        <v>22330051920314</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -4806,22 +4806,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920419</v>
+        <v>22330051920314</v>
       </c>
       <c r="B11" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="E11" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4829,22 +4829,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920308</v>
+        <v>22330051920315</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="E12" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4852,22 +4852,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920308</v>
+        <v>22330051920315</v>
       </c>
       <c r="B13" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="C13" t="s">
-        <v>78</v>
+        <v>115</v>
       </c>
       <c r="D13" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="E13" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4875,22 +4875,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920397</v>
+        <v>22330051920290</v>
       </c>
       <c r="B14" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="C14" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="D14" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="E14" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920397</v>
+        <v>22330051920412</v>
       </c>
       <c r="B15" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C15" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920314</v>
+        <v>22330051920360</v>
       </c>
       <c r="B16" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="C16" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="D16" t="s">
-        <v>148</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4944,22 +4944,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920314</v>
+        <v>22330051920297</v>
       </c>
       <c r="B17" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D17" t="s">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G17">
         <v>5</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920315</v>
+        <v>22330051920298</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C18" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D18" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G18">
         <v>5</v>
@@ -4990,16 +4990,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920315</v>
+        <v>22330051920302</v>
       </c>
       <c r="B19" t="s">
-        <v>96</v>
+        <v>77</v>
       </c>
       <c r="C19" t="s">
-        <v>115</v>
+        <v>93</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>130</v>
       </c>
       <c r="E19" t="s">
         <v>7</v>
@@ -5013,16 +5013,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920290</v>
+        <v>22330051920303</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>131</v>
       </c>
       <c r="E20" t="s">
         <v>6</v>
@@ -5036,22 +5036,22 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920360</v>
+        <v>22330051920308</v>
       </c>
       <c r="B21" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C21" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G21">
         <v>5</v>
@@ -5059,16 +5059,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920297</v>
+        <v>22330051920311</v>
       </c>
       <c r="B22" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D22" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E22" t="s">
         <v>6</v>
@@ -5082,16 +5079,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920298</v>
+        <v>22330051920408</v>
       </c>
       <c r="B23" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D23" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E23" t="s">
         <v>5</v>
@@ -5105,113 +5102,24 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>22330051920302</v>
+        <v>22330051920373</v>
       </c>
       <c r="B24" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C24" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D24" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E24" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920311</v>
-      </c>
-      <c r="B25" t="s">
-        <v>86</v>
-      </c>
-      <c r="D25" t="s">
-        <v>140</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>57</v>
-      </c>
-      <c r="G25">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920312</v>
-      </c>
-      <c r="B26" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" t="s">
-        <v>109</v>
-      </c>
-      <c r="D26" t="s">
-        <v>141</v>
-      </c>
-      <c r="E26" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" t="s">
-        <v>60</v>
-      </c>
-      <c r="G26">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920408</v>
-      </c>
-      <c r="B27" t="s">
-        <v>93</v>
-      </c>
-      <c r="C27" t="s">
-        <v>112</v>
-      </c>
-      <c r="D27" t="s">
-        <v>137</v>
-      </c>
-      <c r="E27" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" t="s">
-        <v>56</v>
-      </c>
-      <c r="G27">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920373</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>113</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>5</v>
-      </c>
-      <c r="F28" t="s">
-        <v>56</v>
-      </c>
-      <c r="G28">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -992,7 +992,7 @@
         <v>-1</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P4">
         <v>4</v>
@@ -1069,7 +1069,7 @@
         <v>-1</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P5">
         <v>6</v>
@@ -1087,7 +1087,7 @@
         <v>6</v>
       </c>
       <c r="U5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V5">
         <v>7</v>
@@ -1146,7 +1146,7 @@
         <v>-1</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
         <v>6</v>
@@ -1164,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="U6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1223,7 +1223,7 @@
         <v>-1</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1300,7 +1300,7 @@
         <v>-1</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P8">
         <v>7</v>
@@ -1377,7 +1377,7 @@
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>7</v>
@@ -1454,7 +1454,7 @@
         <v>-1</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>7</v>
@@ -1472,7 +1472,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1531,7 +1531,7 @@
         <v>-1</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>7</v>
@@ -1608,7 +1608,7 @@
         <v>-1</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
         <v>7</v>
@@ -1685,7 +1685,7 @@
         <v>-1</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -1762,7 +1762,7 @@
         <v>-1</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>6</v>
@@ -1839,7 +1839,7 @@
         <v>-1</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P15">
         <v>6</v>
@@ -1916,7 +1916,7 @@
         <v>-1</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>7</v>
@@ -1993,7 +1993,7 @@
         <v>-1</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
         <v>6</v>
@@ -2070,7 +2070,7 @@
         <v>-1</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>5</v>
@@ -2088,7 +2088,7 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V18">
         <v>5</v>
@@ -2147,7 +2147,7 @@
         <v>-1</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>7</v>
@@ -2224,7 +2224,7 @@
         <v>-1</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
         <v>7</v>
@@ -2242,7 +2242,7 @@
         <v>7</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>6</v>
@@ -2301,7 +2301,7 @@
         <v>-1</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
         <v>7</v>
@@ -2378,7 +2378,7 @@
         <v>-1</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
         <v>5</v>
@@ -2455,7 +2455,7 @@
         <v>-1</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
         <v>7</v>
@@ -2532,7 +2532,7 @@
         <v>-1</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P24">
         <v>6</v>
@@ -2609,7 +2609,7 @@
         <v>-1</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P25">
         <v>7</v>
@@ -2686,7 +2686,7 @@
         <v>-1</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
         <v>5</v>
@@ -2763,7 +2763,7 @@
         <v>-1</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P27">
         <v>7</v>
@@ -2840,7 +2840,7 @@
         <v>-1</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P28">
         <v>7</v>
@@ -2858,7 +2858,7 @@
         <v>8</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>7</v>
@@ -2917,7 +2917,7 @@
         <v>-1</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
         <v>5</v>
@@ -2994,7 +2994,7 @@
         <v>-1</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P30">
         <v>8</v>
@@ -3071,7 +3071,7 @@
         <v>-1</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>7</v>
@@ -3148,7 +3148,7 @@
         <v>-1</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
         <v>5</v>
@@ -3225,7 +3225,7 @@
         <v>-1</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
         <v>6</v>
@@ -3243,7 +3243,7 @@
         <v>5</v>
       </c>
       <c r="U33">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>6</v>
@@ -3302,7 +3302,7 @@
         <v>-1</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>5</v>
@@ -3320,7 +3320,7 @@
         <v>5</v>
       </c>
       <c r="U34">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V34">
         <v>5</v>
@@ -3379,7 +3379,7 @@
         <v>-1</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P35">
         <v>7</v>
@@ -3397,7 +3397,7 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V35">
         <v>5</v>
@@ -3456,7 +3456,7 @@
         <v>-1</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>7</v>
@@ -3533,7 +3533,7 @@
         <v>-1</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>6</v>
@@ -3610,7 +3610,7 @@
         <v>-1</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P38">
         <v>6</v>
@@ -3628,7 +3628,7 @@
         <v>7</v>
       </c>
       <c r="U38">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V38">
         <v>5</v>
@@ -3737,19 +3737,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F3">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="G3">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4567,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4599,16 +4599,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920291</v>
+        <v>22330051920307</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C2" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D2" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -4622,16 +4622,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920291</v>
+        <v>22330051920307</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -4645,16 +4645,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -4668,16 +4668,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920307</v>
+        <v>22330051920419</v>
       </c>
       <c r="B5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
         <v>6</v>
@@ -4691,16 +4691,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920419</v>
+        <v>22330051920397</v>
       </c>
       <c r="B6" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C6" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
@@ -4714,22 +4714,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920419</v>
+        <v>22330051920397</v>
       </c>
       <c r="B7" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="C7" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4737,16 +4737,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920397</v>
+        <v>22330051920314</v>
       </c>
       <c r="B8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E8" t="s">
         <v>5</v>
@@ -4760,22 +4760,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920397</v>
+        <v>22330051920314</v>
       </c>
       <c r="B9" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>114</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4783,16 +4783,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920314</v>
+        <v>22330051920291</v>
       </c>
       <c r="B10" t="s">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="C10" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="E10" t="s">
         <v>5</v>
@@ -4806,22 +4806,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920314</v>
+        <v>22330051920412</v>
       </c>
       <c r="B11" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="D11" t="s">
-        <v>148</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G11">
         <v>5</v>
@@ -4829,16 +4829,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920315</v>
+        <v>22330051920297</v>
       </c>
       <c r="B12" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="C12" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="D12" t="s">
-        <v>149</v>
+        <v>124</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -4852,22 +4852,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920315</v>
+        <v>22330051920298</v>
       </c>
       <c r="B13" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C13" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D13" t="s">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4875,22 +4875,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920290</v>
+        <v>22330051920302</v>
       </c>
       <c r="B14" t="s">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="C14" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D14" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G14">
         <v>5</v>
@@ -4898,22 +4898,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920412</v>
+        <v>22330051920303</v>
       </c>
       <c r="B15" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>100</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="E15" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -4921,22 +4921,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920360</v>
+        <v>22330051920308</v>
       </c>
       <c r="B16" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="D16" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E16" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G16">
         <v>5</v>
@@ -4944,16 +4944,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920297</v>
+        <v>22330051920311</v>
       </c>
       <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D17" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -4967,16 +4964,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920298</v>
+        <v>22330051920408</v>
       </c>
       <c r="B18" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C18" t="s">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="D18" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
@@ -4990,22 +4987,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920302</v>
+        <v>22330051920373</v>
       </c>
       <c r="B19" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="C19" t="s">
-        <v>93</v>
+        <v>113</v>
       </c>
       <c r="D19" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="E19" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G19">
         <v>5</v>
@@ -5013,113 +5010,24 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920303</v>
+        <v>22330051920315</v>
       </c>
       <c r="B20" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="E20" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920308</v>
-      </c>
-      <c r="B21" t="s">
-        <v>84</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" t="s">
-        <v>91</v>
-      </c>
-      <c r="E21" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" t="s">
-        <v>56</v>
-      </c>
-      <c r="G21">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920311</v>
-      </c>
-      <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="D22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>57</v>
-      </c>
-      <c r="G22">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920408</v>
-      </c>
-      <c r="B23" t="s">
-        <v>93</v>
-      </c>
-      <c r="C23" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" t="s">
-        <v>56</v>
-      </c>
-      <c r="G23">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920373</v>
-      </c>
-      <c r="B24" t="s">
-        <v>94</v>
-      </c>
-      <c r="C24" t="s">
-        <v>113</v>
-      </c>
-      <c r="D24" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" t="s">
-        <v>56</v>
-      </c>
-      <c r="G24">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -188,16 +188,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Medina Tolentino Francisco</t>
+  </si>
+  <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Jiménez Nieto Enrique</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Medina Tolentino Francisco</t>
-  </si>
-  <si>
-    <t>Gaspar Velazco Juan Francisco</t>
-  </si>
-  <si>
-    <t>Jiménez Nieto Enrique</t>
   </si>
   <si>
     <t>Contreras Díaz Irma Ivette</t>
@@ -989,7 +989,7 @@
         <v>5</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>5</v>
@@ -1066,7 +1066,7 @@
         <v>6</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
         <v>8</v>
@@ -1143,7 +1143,7 @@
         <v>6</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O6">
         <v>7</v>
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U6">
         <v>6</v>
@@ -1220,7 +1220,7 @@
         <v>8</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O7">
         <v>8</v>
@@ -1297,7 +1297,7 @@
         <v>6</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O8">
         <v>7</v>
@@ -1374,7 +1374,7 @@
         <v>10</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
         <v>8</v>
@@ -1392,7 +1392,7 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
         <v>7</v>
@@ -1451,7 +1451,7 @@
         <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
         <v>7</v>
@@ -1528,7 +1528,7 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>10</v>
@@ -1605,7 +1605,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
         <v>6</v>
@@ -1682,7 +1682,7 @@
         <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O13">
         <v>6</v>
@@ -1700,7 +1700,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1759,7 +1759,7 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>7</v>
@@ -1836,7 +1836,7 @@
         <v>8</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
         <v>7</v>
@@ -1913,7 +1913,7 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
         <v>7</v>
@@ -1990,7 +1990,7 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O17">
         <v>7</v>
@@ -2067,7 +2067,7 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O18">
         <v>9</v>
@@ -2085,7 +2085,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -2144,7 +2144,7 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
         <v>6</v>
@@ -2221,7 +2221,7 @@
         <v>7</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
         <v>9</v>
@@ -2298,7 +2298,7 @@
         <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O21">
         <v>6</v>
@@ -2375,7 +2375,7 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
         <v>6</v>
@@ -2393,7 +2393,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U22">
         <v>5</v>
@@ -2452,7 +2452,7 @@
         <v>10</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>7</v>
@@ -2529,7 +2529,7 @@
         <v>6</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
         <v>6</v>
@@ -2547,7 +2547,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2606,7 +2606,7 @@
         <v>6</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O25">
         <v>6</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -2683,7 +2683,7 @@
         <v>6</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
         <v>8</v>
@@ -2701,7 +2701,7 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U26">
         <v>7</v>
@@ -2760,7 +2760,7 @@
         <v>8</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O27">
         <v>7</v>
@@ -2837,7 +2837,7 @@
         <v>10</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
         <v>6</v>
@@ -2855,7 +2855,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U28">
         <v>7</v>
@@ -2914,7 +2914,7 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O29">
         <v>7</v>
@@ -2991,7 +2991,7 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
         <v>10</v>
@@ -3068,7 +3068,7 @@
         <v>9</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O31">
         <v>7</v>
@@ -3145,7 +3145,7 @@
         <v>6</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O32">
         <v>6</v>
@@ -3163,7 +3163,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U32">
         <v>5</v>
@@ -3222,7 +3222,7 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O33">
         <v>5</v>
@@ -3240,7 +3240,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U33">
         <v>7</v>
@@ -3299,7 +3299,7 @@
         <v>5</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O34">
         <v>6</v>
@@ -3317,7 +3317,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U34">
         <v>8</v>
@@ -3376,7 +3376,7 @@
         <v>6</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O35">
         <v>8</v>
@@ -3394,7 +3394,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U35">
         <v>7</v>
@@ -3453,7 +3453,7 @@
         <v>7</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
         <v>7</v>
@@ -3471,7 +3471,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3530,7 +3530,7 @@
         <v>5</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O37">
         <v>7</v>
@@ -3548,7 +3548,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3607,7 +3607,7 @@
         <v>6</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O38">
         <v>7</v>
@@ -3696,7 +3696,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>56</v>
@@ -3705,19 +3705,19 @@
         <v>36</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F2">
-        <v>61.11</v>
+        <v>77.78</v>
       </c>
       <c r="G2">
-        <v>38.89</v>
+        <v>22.22</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -3728,7 +3728,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>57</v>
@@ -3737,19 +3737,19 @@
         <v>36</v>
       </c>
       <c r="D3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>77.78</v>
+        <v>80.56</v>
       </c>
       <c r="G3">
-        <v>22.22</v>
+        <v>19.44</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3760,7 +3760,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>58</v>
@@ -3769,19 +3769,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>80.56</v>
+        <v>88.89</v>
       </c>
       <c r="G4">
-        <v>19.44</v>
+        <v>11.11</v>
       </c>
       <c r="H4">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3792,7 +3792,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>59</v>
@@ -3801,19 +3801,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>88.89</v>
+        <v>97.22</v>
       </c>
       <c r="G5">
-        <v>11.11</v>
+        <v>2.78</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4567,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4599,19 +4599,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920307</v>
+        <v>22330051920370</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C2" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>56</v>
@@ -4622,19 +4622,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920307</v>
+        <v>22330051920370</v>
       </c>
       <c r="B3" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" t="s">
         <v>57</v>
@@ -4645,22 +4645,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920419</v>
+        <v>22330051920418</v>
       </c>
       <c r="B4" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D4" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920419</v>
+        <v>22330051920418</v>
       </c>
       <c r="B5" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C5" t="s">
-        <v>105</v>
+        <v>80</v>
       </c>
       <c r="D5" t="s">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4691,19 +4691,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920397</v>
+        <v>22330051920297</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>102</v>
       </c>
       <c r="D6" t="s">
-        <v>146</v>
+        <v>124</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
         <v>56</v>
@@ -4714,22 +4714,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920397</v>
+        <v>22330051920302</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D7" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4737,19 +4737,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920314</v>
+        <v>22330051920303</v>
       </c>
       <c r="B8" t="s">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="C8" t="s">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
         <v>56</v>
@@ -4760,22 +4760,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920314</v>
+        <v>22330051920307</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="C9" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D9" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4783,19 +4783,19 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920291</v>
+        <v>22330051920419</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="C10" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="D10" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="E10" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
         <v>56</v>
@@ -4806,19 +4806,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920412</v>
+        <v>22330051920311</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>100</v>
+        <v>86</v>
       </c>
       <c r="D11" t="s">
-        <v>121</v>
+        <v>140</v>
       </c>
       <c r="E11" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
         <v>56</v>
@@ -4829,19 +4826,19 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920297</v>
+        <v>22330051920397</v>
       </c>
       <c r="B12" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>124</v>
+        <v>146</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
         <v>57</v>
@@ -4852,22 +4849,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920298</v>
+        <v>22330051920314</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="C13" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="D13" t="s">
-        <v>126</v>
+        <v>148</v>
       </c>
       <c r="E13" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4875,159 +4872,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920302</v>
+        <v>22330051920315</v>
       </c>
       <c r="B14" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>115</v>
       </c>
       <c r="D14" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920303</v>
-      </c>
-      <c r="B15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C15" t="s">
-        <v>72</v>
-      </c>
-      <c r="D15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>57</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920308</v>
-      </c>
-      <c r="B16" t="s">
-        <v>84</v>
-      </c>
-      <c r="C16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D16" t="s">
-        <v>91</v>
-      </c>
-      <c r="E16" t="s">
-        <v>5</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920311</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" t="s">
-        <v>140</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>57</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920408</v>
-      </c>
-      <c r="B18" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" t="s">
-        <v>137</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920373</v>
-      </c>
-      <c r="B19" t="s">
-        <v>94</v>
-      </c>
-      <c r="C19" t="s">
-        <v>113</v>
-      </c>
-      <c r="D19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" t="s">
-        <v>5</v>
-      </c>
-      <c r="F19" t="s">
-        <v>56</v>
-      </c>
-      <c r="G19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920315</v>
-      </c>
-      <c r="B20" t="s">
-        <v>96</v>
-      </c>
-      <c r="C20" t="s">
-        <v>115</v>
-      </c>
-      <c r="D20" t="s">
-        <v>149</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20">
         <v>5</v>
       </c>
     </row>

--- a/grupos/1EV - Estadisticos 20221.xlsx
+++ b/grupos/1EV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -1004,7 +1004,7 @@
         <v>7</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T4">
         <v>5</v>
@@ -1081,7 +1081,7 @@
         <v>8</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
         <v>6</v>
@@ -1099,7 +1099,7 @@
         <v>8</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1158,7 +1158,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T6">
         <v>6</v>
@@ -1235,7 +1235,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>8</v>
@@ -1312,7 +1312,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T8">
         <v>6</v>
@@ -1389,7 +1389,7 @@
         <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T9">
         <v>6</v>
@@ -1466,7 +1466,7 @@
         <v>9</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1484,7 +1484,7 @@
         <v>9</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1543,7 +1543,7 @@
         <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T11">
         <v>7</v>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1620,7 +1620,7 @@
         <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T12">
         <v>6</v>
@@ -1697,7 +1697,7 @@
         <v>7</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1774,7 +1774,7 @@
         <v>10</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>9</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T15">
         <v>6</v>
@@ -1869,7 +1869,7 @@
         <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1928,7 +1928,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>7</v>
@@ -1946,7 +1946,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -2005,7 +2005,7 @@
         <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -2082,7 +2082,7 @@
         <v>6</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -2100,7 +2100,7 @@
         <v>6</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T19">
         <v>7</v>
@@ -2177,7 +2177,7 @@
         <v>6</v>
       </c>
       <c r="Y19">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2236,7 +2236,7 @@
         <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>7</v>
@@ -2313,7 +2313,7 @@
         <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
@@ -2331,7 +2331,7 @@
         <v>9</v>
       </c>
       <c r="Y21">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2390,7 +2390,7 @@
         <v>9</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T22">
         <v>6</v>
@@ -2408,7 +2408,7 @@
         <v>7</v>
       </c>
       <c r="Y22">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2467,7 +2467,7 @@
         <v>10</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>8</v>
@@ -2485,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2544,7 +2544,7 @@
         <v>7</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T24">
         <v>6</v>
@@ -2621,7 +2621,7 @@
         <v>8</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T25">
         <v>6</v>
@@ -2698,7 +2698,7 @@
         <v>8</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
         <v>6</v>
@@ -2775,7 +2775,7 @@
         <v>9</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2793,7 +2793,7 @@
         <v>9</v>
       </c>
       <c r="Y27">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2852,7 +2852,7 @@
         <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>9</v>
@@ -2929,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T29">
         <v>6</v>
@@ -2947,7 +2947,7 @@
         <v>6</v>
       </c>
       <c r="Y29">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -3006,7 +3006,7 @@
         <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -3083,7 +3083,7 @@
         <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -3160,7 +3160,7 @@
         <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T32">
         <v>6</v>
@@ -3237,7 +3237,7 @@
         <v>7</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T33">
         <v>6</v>
@@ -3314,7 +3314,7 @@
         <v>8</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
         <v>6</v>
@@ -3391,7 +3391,7 @@
         <v>8</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T35">
         <v>6</v>
@@ -3468,7 +3468,7 @@
         <v>10</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3545,7 +3545,7 @@
         <v>7</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>6</v>
@@ -3563,7 +3563,7 @@
         <v>6</v>
       </c>
       <c r="Y37">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:25">
@@ -3622,7 +3622,7 @@
         <v>8</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T38">
         <v>7</v>
@@ -3769,19 +3769,19 @@
         <v>36</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>88.89</v>
+        <v>94.44</v>
       </c>
       <c r="G4">
-        <v>11.11</v>
+        <v>5.56</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -4567,7 +4567,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4599,16 +4599,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920370</v>
+        <v>22330051920417</v>
       </c>
       <c r="B2" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -4622,16 +4622,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920370</v>
+        <v>22330051920417</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -4645,22 +4645,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920418</v>
+        <v>22330051920370</v>
       </c>
       <c r="B4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4668,22 +4668,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920418</v>
+        <v>22330051920370</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -4691,22 +4691,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920297</v>
+        <v>22330051920418</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -4714,22 +4714,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920302</v>
+        <v>22330051920418</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -4737,16 +4737,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920303</v>
+        <v>22330051920297</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>102</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -4760,22 +4760,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920307</v>
+        <v>22330051920302</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C9" t="s">
-        <v>107</v>
+        <v>93</v>
       </c>
       <c r="D9" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -4783,16 +4783,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920419</v>
+        <v>22330051920303</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="D10" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -4806,13 +4806,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920311</v>
+        <v>22330051920307</v>
       </c>
       <c r="B11" t="s">
-        <v>86</v>
+        <v>81</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -4826,22 +4829,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920397</v>
+        <v>22330051920419</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G12">
         <v>5</v>
@@ -4849,22 +4852,19 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920314</v>
+        <v>22330051920311</v>
       </c>
       <c r="B13" t="s">
-        <v>95</v>
-      </c>
-      <c r="C13" t="s">
-        <v>114</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -4872,16 +4872,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920315</v>
+        <v>22330051920397</v>
       </c>
       <c r="B14" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="C14" t="s">
-        <v>115</v>
+        <v>90</v>
       </c>
       <c r="D14" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
         <v>7</v>
@@ -4890,6 +4890,29 @@
         <v>57</v>
       </c>
       <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920315</v>
+      </c>
+      <c r="B15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" t="s">
+        <v>149</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>57</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>
